--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>١‏/١٠‏/٢٠٢٦، ٤:١٩:٤١ ص</v>
+        <v>١‏/١٠‏/٢٠٢٦، ٩:٢٨:٢٠ م</v>
       </c>
     </row>
     <row r="6">
@@ -1043,7 +1043,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.7.0</v>
+        <v>6.7.2</v>
       </c>
     </row>
     <row r="11">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>١‏/١٠‏/٢٠٢٦، ٩:٢٨:٢٠ م</v>
+        <v>١‏/١٠‏/٢٠٢٦، ١٠:٠٢:٤٧ م</v>
       </c>
     </row>
     <row r="6">
@@ -1043,7 +1043,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.7.2</v>
+        <v>6.8.0</v>
       </c>
     </row>
     <row r="11">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>١‏/١٠‏/٢٠٢٦، ١٠:٠٢:٤٧ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٨:٥٩:٤١ ص</v>
       </c>
     </row>
     <row r="6">
@@ -1043,7 +1043,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.8.0</v>
+        <v>6.9.0</v>
       </c>
     </row>
     <row r="11">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١٠:١٦:٤٢ ص</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١١:٠٠:١٠ ص</v>
       </c>
     </row>
     <row r="6">
@@ -1043,7 +1043,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.1</v>
+        <v>6.9.3</v>
       </c>
     </row>
     <row r="11">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١١:٠٠:١٠ ص</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١١:٢٩:٥٤ ص</v>
       </c>
     </row>
     <row r="6">
@@ -1043,7 +1043,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.3</v>
+        <v>6.9.4</v>
       </c>
     </row>
     <row r="11">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١١:٢٩:٥٤ ص</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٠٣:٢٩ م</v>
       </c>
     </row>
     <row r="6">
@@ -1043,7 +1043,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.4</v>
+        <v>6.9.5</v>
       </c>
     </row>
     <row r="11">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٠٣:٢٩ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٢٨:٠٣ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٢٨:٠٣ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٥٨:٠٣ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١٢:٥٨:٠٣ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ١:١٨:٣٦ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ١:١٨:٣٦ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٢:٥١:٣٠ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٢:٥١:٣٠ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٣:٣٥:١٦ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٣:٣٥:١٦ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٣:٥٠:٠٢ م</v>
       </c>
     </row>
     <row r="6">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٣:٥٠:٠٢ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٥:٥٤:٠٥ م</v>
       </c>
     </row>
     <row r="6">
@@ -1043,7 +1043,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.5</v>
+        <v>6.9.13</v>
       </c>
     </row>
     <row r="11">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٥:٥٤:٠٥ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٦:٣١:١٧ م</v>
       </c>
     </row>
     <row r="6">
@@ -1043,7 +1043,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.13</v>
+        <v>6.9.14</v>
       </c>
     </row>
     <row r="11">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -416,10 +416,10 @@
   <dimension ref="A1:I2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.83203125" customWidth="1"/>
@@ -431,16 +431,16 @@
         <v>الصف/الشعبة</v>
       </c>
       <c r="B1" t="str">
-        <v>طلاب فريدون</v>
+        <v>عدد الطلاب</v>
       </c>
       <c r="C1" t="str">
-        <v>نتائج مقيمة</v>
+        <v>حاضر/مقيم</v>
       </c>
       <c r="D1" t="str">
-        <v>نتائج ناجحة</v>
+        <v>ناجح</v>
       </c>
       <c r="E1" t="str">
-        <v>نتائج راسبة</v>
+        <v>راسب</v>
       </c>
       <c r="F1" t="str">
         <v>نسبة النجاح</v>
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٦:٣١:١٧ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٧:١٧:٥٩ م</v>
       </c>
     </row>
     <row r="6">
@@ -1043,7 +1043,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.14</v>
+        <v>6.9.15</v>
       </c>
     </row>
     <row r="11">

--- a/source/tests/output/roundtrip.xlsx
+++ b/source/tests/output/roundtrip.xlsx
@@ -1003,7 +1003,7 @@
         <v>وقت التصدير</v>
       </c>
       <c r="B5" t="str">
-        <v>٢‏/١٠‏/٢٠٢٦، ٧:١٧:٥٩ م</v>
+        <v>٢‏/١٠‏/٢٠٢٦، ٧:٤٩:١٧ م</v>
       </c>
     </row>
     <row r="6">
@@ -1043,7 +1043,7 @@
         <v>الإصدار</v>
       </c>
       <c r="B10" t="str">
-        <v>6.9.15</v>
+        <v>6.9.16</v>
       </c>
     </row>
     <row r="11">
